--- a/nirmaan_stack/services/boq_parser/tests/fixtures/synthetic_multi_area_2row.xlsx
+++ b/nirmaan_stack/services/boq_parser/tests/fixtures/synthetic_multi_area_2row.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,20 +429,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Block A</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Block B</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -461,30 +466,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -499,22 +509,27 @@
           <t>Electrical works</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Nos</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>500</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>300</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>100</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>800</v>
       </c>
     </row>
@@ -527,22 +542,27 @@
           <t>Civil works</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Nos</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>10</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>1000</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>7</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>700</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>120</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>1700</v>
       </c>
     </row>
@@ -555,29 +575,34 @@
           <t>HVAC works</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Nos</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>200</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>100</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>150</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
